--- a/data/trans_orig/IQ2608_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2608_R3-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>60307</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53115</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66463</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>59921</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>52975</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67985</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>52291</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>67057</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>67,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60307</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>53431</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66425</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110593</t>
+          <t>110512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129899</t>
+          <t>129981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23960</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17804</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31152</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29004</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20940</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35950</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21868</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36634</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>32,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23960</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17842</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30836</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43293</t>
+          <t>43211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62599</t>
+          <t>62680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>284598</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>268427</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>302585</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>60,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>57,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>64,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>369</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>242642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>226003</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>257863</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>226532</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>258517</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>59,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>284598</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>267151</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>300056</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>60,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>506981</t>
+          <t>503784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>551958</t>
+          <t>548014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>184152</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>200323</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>163772</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148551</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>180411</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>147897</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>179882</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>40,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>184152</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>168694</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>201599</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>39,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323206</t>
+          <t>327150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368183</t>
+          <t>371380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>468750</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>468750</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>468750</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>468750</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>468750</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>468750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103881</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95326</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>113256</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>62,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100110</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>89907</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>111268</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>90212</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>110363</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>59,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>103881</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93623</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112777</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189834</t>
+          <t>189304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216886</t>
+          <t>218588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49643</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40268</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58198</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69213</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58055</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>79416</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58960</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>49643</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>40747</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>59901</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,34%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105961</t>
+          <t>104259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133013</t>
+          <t>133543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>448785</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>429185</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>469225</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>382463</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>421897</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>383130</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>422022</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>448785</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>430323</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>470060</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>820057</t>
+          <t>822803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>878872</t>
+          <t>880336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>257756</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>237316</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>277356</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>386</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>261989</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>242766</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>282200</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>242641</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>281533</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>39,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>257756</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>236481</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>276218</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>492332</t>
+          <t>490868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>551147</t>
+          <t>548401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>706541</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>706541</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>706541</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>706541</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>706541</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>706541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69322</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61616</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74775</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>73264</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66616</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>78831</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>67086</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>78700</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>81,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69322</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>62941</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>74732</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>81,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132933</t>
+          <t>133569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150803</t>
+          <t>150705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16242</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10789</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23948</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16856</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11289</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23504</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11420</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23034</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16242</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10832</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22623</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42751</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>383385</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>369913</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>396562</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>83,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>502</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>347852</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>333922</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>361933</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>333545</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>361264</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>383385</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>369394</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>398607</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>80,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>710975</t>
+          <t>709879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>751179</t>
+          <t>750689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93066</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79889</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106538</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>91552</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77471</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105482</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>78140</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>105859</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93066</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>77844</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>107057</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164676</t>
+          <t>165166</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204880</t>
+          <t>205976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476451</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476451</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476451</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>439404</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>439404</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>439404</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476451</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476451</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>140871</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132689</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>146981</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136616</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>128088</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>143556</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>128559</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>143672</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>85,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>140871</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>132666</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>147507</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266276</t>
+          <t>265862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286452</t>
+          <t>287291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -3130,67 +3130,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>22565</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16455</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30747</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>23572</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16632</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32100</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16516</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>31629</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>14,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22565</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15929</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>30770</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37171</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57347</t>
+          <t>57761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>593578</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>574065</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>609699</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>541099</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>574532</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>538893</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>573373</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>593578</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>576754</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>610092</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1126911</t>
+          <t>1124778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1175280</t>
+          <t>1175478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>131873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>115752</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>151386</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>131980</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>115179</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>148612</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>116338</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>150818</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>131873</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>115359</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>148697</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239882</t>
+          <t>239684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288251</t>
+          <t>290384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>725451</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>725451</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>725451</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>689711</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>725451</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>725451</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>725451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59691</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54223</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63792</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>48805</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43048</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52834</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44031</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52575</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>82,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59691</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>54186</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>63579</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101358</t>
+          <t>101706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114709</t>
+          <t>114506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4822</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14391</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10003</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5974</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15760</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6233</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14777</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8923</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5035</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14428</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>404954</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>390277</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>417514</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>568</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>373872</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>359089</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>387121</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>358774</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>386313</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>80,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>77,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>404954</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>391081</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>417965</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>759387</t>
+          <t>757758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>798157</t>
+          <t>795938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81540</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96217</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>78751</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>106783</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>79559</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>107098</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>19,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>81540</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68529</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95413</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154209</t>
+          <t>156428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>192979</t>
+          <t>194608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>703</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>149151</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139409</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>156861</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>135691</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>126733</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>143319</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>126604</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>143755</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>80,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>75,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>149151</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>139729</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>157276</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271270</t>
+          <t>270651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295885</t>
+          <t>295415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33072</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25362</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42814</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>33169</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25541</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42127</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25105</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>42256</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>19,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33072</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24947</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>42494</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55198</t>
+          <t>55668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79813</t>
+          <t>80432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>596134</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>629014</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>80,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>845</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>541123</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>574331</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>540588</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>573493</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>597211</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>631168</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1148659</t>
+          <t>1149605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1195316</t>
+          <t>1195652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123535</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108318</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141198</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>135172</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>119209</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>152417</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>120047</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>152952</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>19,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>123535</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>106164</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>140121</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235555</t>
+          <t>235219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>282212</t>
+          <t>281266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9717</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9384</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,37%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2676</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>66,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4546</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11256</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11256</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11256</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84090</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>75125</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>93814</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55307</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>47540</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62747</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>62,43%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>53,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92238</t>
+          <t>54267</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80884</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>61959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>147546</t>
+          <t>138357</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134391</t>
+          <t>126479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159599</t>
+          <t>149598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38798</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29074</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47763</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33282</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25842</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41049</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>25620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>40602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>74263</t>
+          <t>72110</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>60869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87418</t>
+          <t>83988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,107 +6218,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24547</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35486</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28525</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23549</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33412</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>28509</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>23402</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33612</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>59267</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>51107</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>67017</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>68,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>58,92%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>77,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31731</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25533</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>36765</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>60256</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>52229</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>67498</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>68,5%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -6331,107 +6331,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12325</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18537</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14723</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9836</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19699</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15146</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10043</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>20253</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>27471</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>19721</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>35631</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>22,74%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12990</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7956</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19188</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>27714</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>20472</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>35741</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>31,5%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>110250</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>133410</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>83202</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>101927</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>97910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210701</t>
+          <t>195323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241588</t>
+          <t>225383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56408</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44955</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68115</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49877</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41166</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59891</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71420</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>109139</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93275</t>
+          <t>92516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124162</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
